--- a/output/laminas_comunales/comunal_o_ocup_a_2021_magallanes.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2021_magallanes.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,16 +375,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>12301</t>
+          <t>12102</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Porvenir</t>
+          <t>Laguna Blanca</t>
         </is>
       </c>
       <c r="C2">
-        <v>45.8203005213125</v>
+        <v>65.0900900900901</v>
       </c>
     </row>
     <row r="3">
@@ -399,52 +399,502 @@
         </is>
       </c>
       <c r="C3">
-        <v>43.5858585858586</v>
+        <v>64.0151515151515</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>12101</t>
+          <t>12301</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Punta Arenas</t>
+          <t>Porvenir</t>
         </is>
       </c>
       <c r="C4">
-        <v>40.6616011649801</v>
+        <v>60.5684833639518</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>12401</t>
+          <t>12101</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Natales</t>
+          <t>Punta Arenas</t>
         </is>
       </c>
       <c r="C5">
-        <v>38.1428849814873</v>
+        <v>57.3440633774569</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>55.3285256410256</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>55.1282051282051</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>53.7594561126028</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>53.3518019367076</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>46.8100722673893</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>45.8203005213125</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>12201</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Cabo de Hornos</t>
         </is>
       </c>
-      <c r="C6">
+      <c r="C12">
+        <v>45.676429567643</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>45.1398767188241</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>44.643576318969</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>44.082383665717</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>44.0344956244488</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>43.5858585858586</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>41.7615307683257</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>40.6798245614035</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>40.6616011649801</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>39.2089093701997</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>39.1896769536185</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>38.1428849814873</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>37.2464253414386</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>35.3472968134622</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C26">
         <v>34.990253411306</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>34.382546232615</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>31.1599256159926</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>29.3918918918919</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>27.046130952381</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>23.7037037037037</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>12102</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Laguna Blanca</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>23.0769230769231</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>12201</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Cabo de Hornos</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>21.420581655481</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>12301</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Porvenir</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>16.6811594202899</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>12101</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Punta Arenas</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>13.5300967395199</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>12401</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Natales</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>10.3230658557321</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_o_ocup_a_2021_magallanes.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2021_magallanes.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -375,16 +375,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>12102</t>
+          <t>12301</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Laguna Blanca</t>
+          <t>Porvenir</t>
         </is>
       </c>
       <c r="C2">
-        <v>65.0900900900901</v>
+        <v>45.8203005213125</v>
       </c>
     </row>
     <row r="3">
@@ -399,502 +399,52 @@
         </is>
       </c>
       <c r="C3">
-        <v>64.0151515151515</v>
+        <v>43.5858585858586</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>12301</t>
+          <t>12101</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Porvenir</t>
+          <t>Punta Arenas</t>
         </is>
       </c>
       <c r="C4">
-        <v>60.5684833639518</v>
+        <v>40.6616011649801</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>12101</t>
+          <t>12401</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Punta Arenas</t>
+          <t>Natales</t>
         </is>
       </c>
       <c r="C5">
-        <v>57.3440633774569</v>
+        <v>38.1428849814873</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>12301</t>
+          <t>12201</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Porvenir</t>
+          <t>Cabo de Hornos</t>
         </is>
       </c>
       <c r="C6">
-        <v>55.3285256410256</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>12102</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Laguna Blanca</t>
-        </is>
-      </c>
-      <c r="C7">
-        <v>55.1282051282051</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>12101</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Punta Arenas</t>
-        </is>
-      </c>
-      <c r="C8">
-        <v>53.7594561126028</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>12401</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Natales</t>
-        </is>
-      </c>
-      <c r="C9">
-        <v>53.3518019367076</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>12301</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Porvenir</t>
-        </is>
-      </c>
-      <c r="C10">
-        <v>46.8100722673893</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>12301</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Porvenir</t>
-        </is>
-      </c>
-      <c r="C11">
-        <v>45.8203005213125</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>12201</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Cabo de Hornos</t>
-        </is>
-      </c>
-      <c r="C12">
-        <v>45.676429567643</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>12401</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Natales</t>
-        </is>
-      </c>
-      <c r="C13">
-        <v>45.1398767188241</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>12301</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Porvenir</t>
-        </is>
-      </c>
-      <c r="C14">
-        <v>44.643576318969</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>12301</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Porvenir</t>
-        </is>
-      </c>
-      <c r="C15">
-        <v>44.082383665717</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>12101</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Punta Arenas</t>
-        </is>
-      </c>
-      <c r="C16">
-        <v>44.0344956244488</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>12102</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Laguna Blanca</t>
-        </is>
-      </c>
-      <c r="C17">
-        <v>43.5858585858586</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>12401</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Natales</t>
-        </is>
-      </c>
-      <c r="C18">
-        <v>41.7615307683257</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>12201</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Cabo de Hornos</t>
-        </is>
-      </c>
-      <c r="C19">
-        <v>40.6798245614035</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>12101</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Punta Arenas</t>
-        </is>
-      </c>
-      <c r="C20">
-        <v>40.6616011649801</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>12201</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Cabo de Hornos</t>
-        </is>
-      </c>
-      <c r="C21">
-        <v>39.2089093701997</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>12401</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Natales</t>
-        </is>
-      </c>
-      <c r="C22">
-        <v>39.1896769536185</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>12401</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Natales</t>
-        </is>
-      </c>
-      <c r="C23">
-        <v>38.1428849814873</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>12101</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Punta Arenas</t>
-        </is>
-      </c>
-      <c r="C24">
-        <v>37.2464253414386</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>12101</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Punta Arenas</t>
-        </is>
-      </c>
-      <c r="C25">
-        <v>35.3472968134622</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>12201</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Cabo de Hornos</t>
-        </is>
-      </c>
-      <c r="C26">
         <v>34.990253411306</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>12401</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Natales</t>
-        </is>
-      </c>
-      <c r="C27">
-        <v>34.382546232615</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>12201</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Cabo de Hornos</t>
-        </is>
-      </c>
-      <c r="C28">
-        <v>31.1599256159926</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>12102</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Laguna Blanca</t>
-        </is>
-      </c>
-      <c r="C29">
-        <v>29.3918918918919</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>12201</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Cabo de Hornos</t>
-        </is>
-      </c>
-      <c r="C30">
-        <v>27.046130952381</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>12102</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Laguna Blanca</t>
-        </is>
-      </c>
-      <c r="C31">
-        <v>23.7037037037037</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>12102</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Laguna Blanca</t>
-        </is>
-      </c>
-      <c r="C32">
-        <v>23.0769230769231</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>12201</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Cabo de Hornos</t>
-        </is>
-      </c>
-      <c r="C33">
-        <v>21.420581655481</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>12301</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Porvenir</t>
-        </is>
-      </c>
-      <c r="C34">
-        <v>16.6811594202899</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>12101</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Punta Arenas</t>
-        </is>
-      </c>
-      <c r="C35">
-        <v>13.5300967395199</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>12401</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Natales</t>
-        </is>
-      </c>
-      <c r="C36">
-        <v>10.3230658557321</v>
       </c>
     </row>
   </sheetData>
